--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New folder\lovable\inventory-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6841C50-EF7E-43A3-8A8B-746F7120AC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA20327D-A0F3-46F4-8361-C08ABE459A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11520" xr2:uid="{F684FE3C-E019-4636-B08A-B3B3339D835A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="363">
   <si>
     <t>Size:Free size;Colour:Cream,Grey,Maroon</t>
   </si>
@@ -1104,9 +1105,6 @@
     <t>Stock</t>
   </si>
   <si>
-    <t xml:space="preserve">Buying Price </t>
-  </si>
-  <si>
     <t>Selling Price</t>
   </si>
   <si>
@@ -1123,6 +1121,9 @@
   </si>
   <si>
     <t xml:space="preserve">Product name </t>
+  </si>
+  <si>
+    <t>Cost</t>
   </si>
 </sst>
 </file>
@@ -1503,25 +1504,25 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G1" t="s">
         <v>362</v>
-      </c>
-      <c r="B1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C1" t="s">
-        <v>360</v>
-      </c>
-      <c r="D1" t="s">
-        <v>359</v>
-      </c>
-      <c r="E1" t="s">
-        <v>358</v>
-      </c>
-      <c r="F1" t="s">
-        <v>357</v>
-      </c>
-      <c r="G1" t="s">
-        <v>356</v>
       </c>
       <c r="H1" t="s">
         <v>355</v>
@@ -1538,7 +1539,7 @@
         <v>60</v>
       </c>
       <c r="C2" t="str">
-        <f>A2</f>
+        <f t="shared" ref="C2:C33" si="0">A2</f>
         <v>1561 Plus size Single Dress</v>
       </c>
       <c r="D2" s="1">
@@ -1565,7 +1566,7 @@
         <v>41</v>
       </c>
       <c r="C3" t="str">
-        <f>A3</f>
+        <f t="shared" si="0"/>
         <v>1609 High low Single Dress</v>
       </c>
       <c r="D3" s="1">
@@ -1592,7 +1593,7 @@
         <v>60</v>
       </c>
       <c r="C4" t="str">
-        <f>A4</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">1625A Single Polka </v>
       </c>
       <c r="D4" s="1">
@@ -1619,7 +1620,7 @@
         <v>60</v>
       </c>
       <c r="C5" t="str">
-        <f>A5</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">1626 Polka Single Dress </v>
       </c>
       <c r="D5" s="1">
@@ -1646,7 +1647,7 @@
         <v>60</v>
       </c>
       <c r="C6" t="str">
-        <f>A6</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">1861 Single Dress Gold line </v>
       </c>
       <c r="D6" s="1">
@@ -1673,7 +1674,7 @@
         <v>60</v>
       </c>
       <c r="C7" t="str">
-        <f>A7</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">1861K 2 Piece Dress Gold Line </v>
       </c>
       <c r="D7" s="1">
@@ -1700,7 +1701,7 @@
         <v>41</v>
       </c>
       <c r="C8" t="str">
-        <f>A8</f>
+        <f t="shared" si="0"/>
         <v>18818 Single Long Sleeved Dress</v>
       </c>
       <c r="D8" s="1">
@@ -1727,7 +1728,7 @@
         <v>60</v>
       </c>
       <c r="C9" t="str">
-        <f>A9</f>
+        <f t="shared" si="0"/>
         <v>18845 Short Single Dress</v>
       </c>
       <c r="D9" s="1">
@@ -1754,7 +1755,7 @@
         <v>323</v>
       </c>
       <c r="C10" t="str">
-        <f>A10</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">2 piece Lace Padded </v>
       </c>
       <c r="D10" s="1">
@@ -1781,7 +1782,7 @@
         <v>323</v>
       </c>
       <c r="C11" t="str">
-        <f>A11</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">2 Piece Silk Set </v>
       </c>
       <c r="D11" s="1">
@@ -1808,7 +1809,7 @@
         <v>323</v>
       </c>
       <c r="C12" t="str">
-        <f>A12</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">2 Piece Silk Set </v>
       </c>
       <c r="D12" s="1">
@@ -1835,7 +1836,7 @@
         <v>180</v>
       </c>
       <c r="C13" t="str">
-        <f>A13</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">2236 Black Button </v>
       </c>
       <c r="D13" s="1">
@@ -1862,7 +1863,7 @@
         <v>180</v>
       </c>
       <c r="C14" t="str">
-        <f>A14</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">2277 Black </v>
       </c>
       <c r="D14" s="1">
@@ -1889,7 +1890,7 @@
         <v>60</v>
       </c>
       <c r="C15" t="str">
-        <f>A15</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">2304 New Kimono </v>
       </c>
       <c r="D15" s="1">
@@ -1916,7 +1917,7 @@
         <v>60</v>
       </c>
       <c r="C16" t="str">
-        <f>A16</f>
+        <f t="shared" si="0"/>
         <v>2411 Long Dress</v>
       </c>
       <c r="D16" s="1">
@@ -1943,7 +1944,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="str">
-        <f>A17</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">3 Piece Set </v>
       </c>
       <c r="D17" s="1">
@@ -1970,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="str">
-        <f>A18</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">3 piece Star </v>
       </c>
       <c r="D18" s="1">
@@ -1997,7 +1998,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <f>A19</f>
+        <f t="shared" si="0"/>
         <v>3/4 Grey Trouser</v>
       </c>
       <c r="D19" s="1">
@@ -2024,7 +2025,7 @@
         <v>299</v>
       </c>
       <c r="C20" t="str">
-        <f>A20</f>
+        <f t="shared" si="0"/>
         <v>3016 Ribbed Jump Suit</v>
       </c>
       <c r="D20" s="1">
@@ -2051,7 +2052,7 @@
         <v>60</v>
       </c>
       <c r="C21" t="str">
-        <f>A21</f>
+        <f t="shared" si="0"/>
         <v>3076 2 Piece Dress</v>
       </c>
       <c r="D21" s="1">
@@ -2078,7 +2079,7 @@
         <v>41</v>
       </c>
       <c r="C22" t="str">
-        <f>A22</f>
+        <f t="shared" si="0"/>
         <v>3078 2 Piece Dress</v>
       </c>
       <c r="D22" s="1">
@@ -2105,7 +2106,7 @@
         <v>60</v>
       </c>
       <c r="C23" t="str">
-        <f>A23</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">3083 2 Piece Dress (Hearts) </v>
       </c>
       <c r="D23" s="1">
@@ -2132,7 +2133,7 @@
         <v>60</v>
       </c>
       <c r="C24" t="str">
-        <f>A24</f>
+        <f t="shared" si="0"/>
         <v>3088 2 Piece Dress (Kisses)</v>
       </c>
       <c r="D24" s="1">
@@ -2159,7 +2160,7 @@
         <v>41</v>
       </c>
       <c r="C25" t="str">
-        <f>A25</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">3091 2 Piece Polka </v>
       </c>
       <c r="D25" s="1">
@@ -2186,7 +2187,7 @@
         <v>10</v>
       </c>
       <c r="C26" t="str">
-        <f>A26</f>
+        <f t="shared" si="0"/>
         <v>3399 2 Piece Trouser</v>
       </c>
       <c r="D26" s="1">
@@ -2213,7 +2214,7 @@
         <v>41</v>
       </c>
       <c r="C27" t="str">
-        <f>A27</f>
+        <f t="shared" si="0"/>
         <v>3485 Long Lace Dress</v>
       </c>
       <c r="D27" s="1">
@@ -2240,7 +2241,7 @@
         <v>159</v>
       </c>
       <c r="C28" t="str">
-        <f>A28</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">5 Piece Set </v>
       </c>
       <c r="D28" s="1">
@@ -2267,7 +2268,7 @@
         <v>60</v>
       </c>
       <c r="C29" t="str">
-        <f>A29</f>
+        <f t="shared" si="0"/>
         <v>6128 Single Dress</v>
       </c>
       <c r="D29" s="1">
@@ -2294,7 +2295,7 @@
         <v>268</v>
       </c>
       <c r="C30" t="str">
-        <f>A30</f>
+        <f t="shared" si="0"/>
         <v>6649 Long Jump Suit</v>
       </c>
       <c r="D30" s="1">
@@ -2321,7 +2322,7 @@
         <v>10</v>
       </c>
       <c r="C31" t="str">
-        <f>A31</f>
+        <f t="shared" si="0"/>
         <v>6657 Shorts Jump Suit</v>
       </c>
       <c r="D31" s="1">
@@ -2348,7 +2349,7 @@
         <v>163</v>
       </c>
       <c r="C32" t="str">
-        <f>A32</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">6730 Seamless </v>
       </c>
       <c r="D32" s="1">
@@ -2375,7 +2376,7 @@
         <v>60</v>
       </c>
       <c r="C33" t="str">
-        <f>A33</f>
+        <f t="shared" si="0"/>
         <v>8143 Single lace Dress</v>
       </c>
       <c r="D33" s="1">
@@ -2402,7 +2403,7 @@
         <v>163</v>
       </c>
       <c r="C34" t="str">
-        <f>A34</f>
+        <f t="shared" ref="C34:C65" si="1">A34</f>
         <v>88351 Lace Panty</v>
       </c>
       <c r="D34" s="1">
@@ -2429,7 +2430,7 @@
         <v>60</v>
       </c>
       <c r="C35" t="str">
-        <f>A35</f>
+        <f t="shared" si="1"/>
         <v>8997 Single Dress</v>
       </c>
       <c r="D35" s="1">
@@ -2456,7 +2457,7 @@
         <v>163</v>
       </c>
       <c r="C36" t="str">
-        <f>A36</f>
+        <f t="shared" si="1"/>
         <v>9054 Lace Panty</v>
       </c>
       <c r="D36" s="1">
@@ -2483,7 +2484,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="str">
-        <f>A37</f>
+        <f t="shared" si="1"/>
         <v>9098 Single Lace Dress</v>
       </c>
       <c r="D37" s="1">
@@ -2510,7 +2511,7 @@
         <v>60</v>
       </c>
       <c r="C38" t="str">
-        <f>A38</f>
+        <f t="shared" si="1"/>
         <v>98037 2 Piece short Hearts</v>
       </c>
       <c r="D38" s="1">
@@ -2537,7 +2538,7 @@
         <v>60</v>
       </c>
       <c r="C39" t="str">
-        <f>A39</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">98042 Maroon Hearts Single Dress </v>
       </c>
       <c r="D39" s="1">
@@ -2564,7 +2565,7 @@
         <v>74</v>
       </c>
       <c r="C40" t="str">
-        <f>A40</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Black Bow Shorts </v>
       </c>
       <c r="D40" s="1">
@@ -2591,7 +2592,7 @@
         <v>235</v>
       </c>
       <c r="C41" t="str">
-        <f>A41</f>
+        <f t="shared" si="1"/>
         <v>Black Bra</v>
       </c>
       <c r="D41" s="1">
@@ -2618,7 +2619,7 @@
         <v>180</v>
       </c>
       <c r="C42" t="str">
-        <f>A42</f>
+        <f t="shared" si="1"/>
         <v>Black Lace</v>
       </c>
       <c r="D42" s="1">
@@ -2645,7 +2646,7 @@
         <v>228</v>
       </c>
       <c r="C43" t="str">
-        <f>A43</f>
+        <f t="shared" si="1"/>
         <v>Body Suit</v>
       </c>
       <c r="D43" s="1">
@@ -2672,7 +2673,7 @@
         <v>45</v>
       </c>
       <c r="C44" t="str">
-        <f>A44</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Bralet </v>
       </c>
       <c r="D44" s="1">
@@ -2699,7 +2700,7 @@
         <v>180</v>
       </c>
       <c r="C45" t="str">
-        <f>A45</f>
+        <f t="shared" si="1"/>
         <v>Brown Bra</v>
       </c>
       <c r="D45" s="1">
@@ -2726,7 +2727,7 @@
         <v>70</v>
       </c>
       <c r="C46" t="str">
-        <f>A46</f>
+        <f t="shared" si="1"/>
         <v>Cami Dress</v>
       </c>
       <c r="D46" s="1">
@@ -2753,7 +2754,7 @@
         <v>74</v>
       </c>
       <c r="C47" t="str">
-        <f>A47</f>
+        <f t="shared" si="1"/>
         <v>Cami Shorts</v>
       </c>
       <c r="D47" s="1">
@@ -2780,7 +2781,7 @@
         <v>74</v>
       </c>
       <c r="C48" t="str">
-        <f>A48</f>
+        <f t="shared" si="1"/>
         <v>Cami shorts + Lace</v>
       </c>
       <c r="D48" s="1">
@@ -2807,7 +2808,7 @@
         <v>18</v>
       </c>
       <c r="C49" t="str">
-        <f>A49</f>
+        <f t="shared" si="1"/>
         <v>Cosmetic Bag</v>
       </c>
       <c r="D49" s="1">
@@ -2834,7 +2835,7 @@
         <v>56</v>
       </c>
       <c r="C50" t="str">
-        <f>A50</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Cotton dress </v>
       </c>
       <c r="D50" s="1">
@@ -2861,7 +2862,7 @@
         <v>203</v>
       </c>
       <c r="C51" t="str">
-        <f>A51</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Cotton Robes </v>
       </c>
       <c r="D51" s="1">
@@ -2888,7 +2889,7 @@
         <v>199</v>
       </c>
       <c r="C52" t="str">
-        <f>A52</f>
+        <f t="shared" si="1"/>
         <v>Cream Stripped</v>
       </c>
       <c r="D52" s="1">
@@ -2915,7 +2916,7 @@
         <v>137</v>
       </c>
       <c r="C53" t="str">
-        <f>A53</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Cross Sandals </v>
       </c>
       <c r="D53" s="1">
@@ -2942,7 +2943,7 @@
         <v>18</v>
       </c>
       <c r="C54" t="str">
-        <f>A54</f>
+        <f t="shared" si="1"/>
         <v>Document Bag</v>
       </c>
       <c r="D54" s="1">
@@ -2969,7 +2970,7 @@
         <v>189</v>
       </c>
       <c r="C55" t="str">
-        <f>A55</f>
+        <f t="shared" si="1"/>
         <v>Eye Mask</v>
       </c>
       <c r="D55" s="1">
@@ -2996,7 +2997,7 @@
         <v>159</v>
       </c>
       <c r="C56" t="str">
-        <f>A56</f>
+        <f t="shared" si="1"/>
         <v>Flowers (2314)</v>
       </c>
       <c r="D56" s="1">
@@ -3023,7 +3024,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="str">
-        <f>A57</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Forest </v>
       </c>
       <c r="D57" s="1">
@@ -3050,7 +3051,7 @@
         <v>180</v>
       </c>
       <c r="C58" t="str">
-        <f>A58</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Grey Lace </v>
       </c>
       <c r="D58" s="1">
@@ -3077,7 +3078,7 @@
         <v>18</v>
       </c>
       <c r="C59" t="str">
-        <f>A59</f>
+        <f t="shared" si="1"/>
         <v>Gym Bag</v>
       </c>
       <c r="D59" s="1">
@@ -3104,7 +3105,7 @@
         <v>173</v>
       </c>
       <c r="C60" t="str">
-        <f>A60</f>
+        <f t="shared" si="1"/>
         <v>Hair Bonnet</v>
       </c>
       <c r="D60" s="1">
@@ -3131,7 +3132,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="str">
-        <f>A61</f>
+        <f t="shared" si="1"/>
         <v>Hearts (wd 227#)</v>
       </c>
       <c r="D61" s="1">
@@ -3158,7 +3159,7 @@
         <v>70</v>
       </c>
       <c r="C62" t="str">
-        <f>A62</f>
+        <f t="shared" si="1"/>
         <v>Lace dress</v>
       </c>
       <c r="D62" s="1">
@@ -3185,7 +3186,7 @@
         <v>163</v>
       </c>
       <c r="C63" t="str">
-        <f>A63</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Lace Panties </v>
       </c>
       <c r="D63" s="1">
@@ -3212,7 +3213,7 @@
         <v>159</v>
       </c>
       <c r="C64" t="str">
-        <f>A64</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Lace trouser </v>
       </c>
       <c r="D64" s="1">
@@ -3239,7 +3240,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="str">
-        <f>A65</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">Last night </v>
       </c>
       <c r="D65" s="1">
@@ -3266,7 +3267,7 @@
         <v>18</v>
       </c>
       <c r="C66" t="str">
-        <f>A66</f>
+        <f t="shared" ref="C66:C97" si="2">A66</f>
         <v xml:space="preserve">Laundry Bag </v>
       </c>
       <c r="D66" s="1">
@@ -3293,7 +3294,7 @@
         <v>70</v>
       </c>
       <c r="C67" t="str">
-        <f>A67</f>
+        <f t="shared" si="2"/>
         <v>Long Dress</v>
       </c>
       <c r="D67" s="1">
@@ -3320,7 +3321,7 @@
         <v>10</v>
       </c>
       <c r="C68" t="str">
-        <f>A68</f>
+        <f t="shared" si="2"/>
         <v>Long Sleeved</v>
       </c>
       <c r="D68" s="1">
@@ -3347,7 +3348,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="str">
-        <f>A69</f>
+        <f t="shared" si="2"/>
         <v>Love Hearts Smiley (7716)</v>
       </c>
       <c r="D69" s="1">
@@ -3374,7 +3375,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="str">
-        <f>A70</f>
+        <f t="shared" si="2"/>
         <v>Maternity Trouser Set</v>
       </c>
       <c r="D70" s="1">
@@ -3401,7 +3402,7 @@
         <v>137</v>
       </c>
       <c r="C71" t="str">
-        <f>A71</f>
+        <f t="shared" si="2"/>
         <v>New Bow</v>
       </c>
       <c r="D71" s="1">
@@ -3428,7 +3429,7 @@
         <v>118</v>
       </c>
       <c r="C72" t="str">
-        <f>A72</f>
+        <f t="shared" si="2"/>
         <v>New Cami Shorts (Vest)</v>
       </c>
       <c r="D72" s="1">
@@ -3455,7 +3456,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="str">
-        <f>A73</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">New Polka with Lace </v>
       </c>
       <c r="D73" s="1">
@@ -3482,7 +3483,7 @@
         <v>74</v>
       </c>
       <c r="C74" t="str">
-        <f>A74</f>
+        <f t="shared" si="2"/>
         <v>New Shorts</v>
       </c>
       <c r="D74" s="1">
@@ -3509,7 +3510,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="str">
-        <f>A75</f>
+        <f t="shared" si="2"/>
         <v>New Star</v>
       </c>
       <c r="D75" s="1">
@@ -3536,7 +3537,7 @@
         <v>56</v>
       </c>
       <c r="C76" t="str">
-        <f>A76</f>
+        <f t="shared" si="2"/>
         <v>No Padding X-back</v>
       </c>
       <c r="D76" s="1">
@@ -3563,7 +3564,7 @@
         <v>118</v>
       </c>
       <c r="C77" t="str">
-        <f>A77</f>
+        <f t="shared" si="2"/>
         <v>Old Collar Shorts</v>
       </c>
       <c r="D77" s="1">
@@ -3590,7 +3591,7 @@
         <v>60</v>
       </c>
       <c r="C78" t="str">
-        <f>A78</f>
+        <f t="shared" si="2"/>
         <v>Onesie</v>
       </c>
       <c r="D78" s="1">
@@ -3617,7 +3618,7 @@
         <v>56</v>
       </c>
       <c r="C79" t="str">
-        <f>A79</f>
+        <f t="shared" si="2"/>
         <v>Padded Dress</v>
       </c>
       <c r="D79" s="1">
@@ -3644,7 +3645,7 @@
         <v>2</v>
       </c>
       <c r="C80" t="str">
-        <f>A80</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">Pink Stripped </v>
       </c>
       <c r="D80" s="1">
@@ -3671,7 +3672,7 @@
         <v>2</v>
       </c>
       <c r="C81" t="str">
-        <f>A81</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">Plain Design </v>
       </c>
       <c r="D81" s="1">
@@ -3698,7 +3699,7 @@
         <v>2</v>
       </c>
       <c r="C82" t="str">
-        <f>A82</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">Plain Set </v>
       </c>
       <c r="D82" s="1">
@@ -3725,7 +3726,7 @@
         <v>2</v>
       </c>
       <c r="C83" t="str">
-        <f>A83</f>
+        <f t="shared" si="2"/>
         <v>Polker Lace</v>
       </c>
       <c r="D83" s="1">
@@ -3752,7 +3753,7 @@
         <v>2</v>
       </c>
       <c r="C84" t="str">
-        <f>A84</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">Round Neck Polker </v>
       </c>
       <c r="D84" s="1">
@@ -3779,7 +3780,7 @@
         <v>2</v>
       </c>
       <c r="C85" t="str">
-        <f>A85</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">Round Neck With Collar Stripe </v>
       </c>
       <c r="D85" s="1">
@@ -3806,7 +3807,7 @@
         <v>92</v>
       </c>
       <c r="C86" t="str">
-        <f>A86</f>
+        <f t="shared" si="2"/>
         <v>Shaper</v>
       </c>
       <c r="D86" s="1">
@@ -3833,7 +3834,7 @@
         <v>70</v>
       </c>
       <c r="C87" t="str">
-        <f>A87</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">Shirt dress </v>
       </c>
       <c r="D87" s="1">
@@ -3860,7 +3861,7 @@
         <v>70</v>
       </c>
       <c r="C88" t="str">
-        <f>A88</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">Shirt dress </v>
       </c>
       <c r="D88" s="1">
@@ -3887,7 +3888,7 @@
         <v>56</v>
       </c>
       <c r="C89" t="str">
-        <f>A89</f>
+        <f t="shared" si="2"/>
         <v>Short Skirt</v>
       </c>
       <c r="D89" s="1">
@@ -3914,7 +3915,7 @@
         <v>10</v>
       </c>
       <c r="C90" t="str">
-        <f>A90</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">Short Sleeved </v>
       </c>
       <c r="D90" s="1">
@@ -3941,7 +3942,7 @@
         <v>2</v>
       </c>
       <c r="C91" t="str">
-        <f>A91</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">Short Sleved Trousers </v>
       </c>
       <c r="D91" s="1">
@@ -3968,7 +3969,7 @@
         <v>74</v>
       </c>
       <c r="C92" t="str">
-        <f>A92</f>
+        <f t="shared" si="2"/>
         <v>Silk Cami Shorts</v>
       </c>
       <c r="D92" s="1">
@@ -3995,7 +3996,7 @@
         <v>70</v>
       </c>
       <c r="C93" t="str">
-        <f>A93</f>
+        <f t="shared" si="2"/>
         <v>Silk Long Dress</v>
       </c>
       <c r="D93" s="1">
@@ -4022,7 +4023,7 @@
         <v>14</v>
       </c>
       <c r="C94" t="str">
-        <f>A94</f>
+        <f t="shared" si="2"/>
         <v>Silk Robes</v>
       </c>
       <c r="D94" s="1">
@@ -4049,7 +4050,7 @@
         <v>2</v>
       </c>
       <c r="C95" t="str">
-        <f>A95</f>
+        <f t="shared" si="2"/>
         <v>Silk Trouser Set</v>
       </c>
       <c r="D95" s="1">
@@ -4076,7 +4077,7 @@
         <v>60</v>
       </c>
       <c r="C96" t="str">
-        <f>A96</f>
+        <f t="shared" si="2"/>
         <v>Single Cute Lace Dress</v>
       </c>
       <c r="D96" s="1">
@@ -4103,7 +4104,7 @@
         <v>56</v>
       </c>
       <c r="C97" t="str">
-        <f>A97</f>
+        <f t="shared" si="2"/>
         <v>Skim Skirts</v>
       </c>
       <c r="D97" s="1">
@@ -4130,7 +4131,7 @@
         <v>52</v>
       </c>
       <c r="C98" t="str">
-        <f>A98</f>
+        <f t="shared" ref="C98:C112" si="3">A98</f>
         <v>Skims Dress</v>
       </c>
       <c r="D98" s="1">
@@ -4157,7 +4158,7 @@
         <v>2</v>
       </c>
       <c r="C99" t="str">
-        <f>A99</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">Smiley  </v>
       </c>
       <c r="D99" s="1">
@@ -4184,7 +4185,7 @@
         <v>45</v>
       </c>
       <c r="C100" t="str">
-        <f>A100</f>
+        <f t="shared" si="3"/>
         <v>Sport Bra</v>
       </c>
       <c r="D100" s="1">
@@ -4211,7 +4212,7 @@
         <v>41</v>
       </c>
       <c r="C101" t="str">
-        <f>A101</f>
+        <f t="shared" si="3"/>
         <v>String Lingerie</v>
       </c>
       <c r="D101" s="1">
@@ -4238,7 +4239,7 @@
         <v>2</v>
       </c>
       <c r="C102" t="str">
-        <f>A102</f>
+        <f t="shared" si="3"/>
         <v>Stripped Design</v>
       </c>
       <c r="D102" s="1">
@@ -4265,7 +4266,7 @@
         <v>35</v>
       </c>
       <c r="C103" t="str">
-        <f>A103</f>
+        <f t="shared" si="3"/>
         <v>Sweater Trouser</v>
       </c>
       <c r="D103" s="1">
@@ -4292,7 +4293,7 @@
         <v>31</v>
       </c>
       <c r="C104" t="str">
-        <f>A104</f>
+        <f t="shared" si="3"/>
         <v>Throw Blankets</v>
       </c>
       <c r="D104" s="1">
@@ -4319,7 +4320,7 @@
         <v>2</v>
       </c>
       <c r="C105" t="str">
-        <f>A105</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">Trouser with Bow </v>
       </c>
       <c r="D105" s="1">
@@ -4346,7 +4347,7 @@
         <v>2</v>
       </c>
       <c r="C106" t="str">
-        <f>A106</f>
+        <f t="shared" si="3"/>
         <v>Trouser With Lace</v>
       </c>
       <c r="D106" s="1">
@@ -4373,7 +4374,7 @@
         <v>2</v>
       </c>
       <c r="C107" t="str">
-        <f>A107</f>
+        <f t="shared" si="3"/>
         <v>VELVET TROUSER</v>
       </c>
       <c r="D107" s="1">
@@ -4400,7 +4401,7 @@
         <v>18</v>
       </c>
       <c r="C108" t="str">
-        <f>A108</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">Wash Bag </v>
       </c>
       <c r="D108" s="1">
@@ -4427,7 +4428,7 @@
         <v>14</v>
       </c>
       <c r="C109" t="str">
-        <f>A109</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">Woolen Robes </v>
       </c>
       <c r="D109" s="1">
@@ -4454,7 +4455,7 @@
         <v>10</v>
       </c>
       <c r="C110" t="str">
-        <f>A110</f>
+        <f t="shared" si="3"/>
         <v>Woolen Sweater</v>
       </c>
       <c r="D110" s="1">
@@ -4481,7 +4482,7 @@
         <v>6</v>
       </c>
       <c r="C111" t="str">
-        <f>A111</f>
+        <f t="shared" si="3"/>
         <v>Woolen Sweaters</v>
       </c>
       <c r="D111" s="1">
@@ -4508,7 +4509,7 @@
         <v>2</v>
       </c>
       <c r="C112" t="str">
-        <f>A112</f>
+        <f t="shared" si="3"/>
         <v>Woolen Trouser</v>
       </c>
       <c r="D112" s="1">
@@ -4525,6 +4526,159 @@
       </c>
       <c r="I112" t="s">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7CB9FD9-D1BF-440E-8530-141419741654}">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
